--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,24 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>V1.8_20260613173932_DRB</t>
         </is>
       </c>
